--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -11285,25 +11285,25 @@
         <v>46283</v>
       </c>
       <c r="B419" t="n">
-        <v>17340</v>
+        <v>17300</v>
       </c>
       <c r="C419" t="n">
-        <v>480057</v>
+        <v>1801460</v>
       </c>
       <c r="D419" t="n">
-        <v>18696</v>
+        <v>18576</v>
       </c>
       <c r="E419" t="n">
-        <v>18513</v>
+        <v>18328</v>
       </c>
       <c r="F419" t="n">
-        <v>17705</v>
+        <v>17569</v>
       </c>
       <c r="G419" t="n">
-        <v>18305</v>
+        <v>18158</v>
       </c>
       <c r="H419" t="n">
-        <v>-0.09911905113440622</v>
+        <v>-0.1063536591367685</v>
       </c>
     </row>
   </sheetData>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H419"/>
+  <dimension ref="A1:H420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11306,6 +11306,32 @@
         <v>-0.1063536591367685</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B420" t="n">
+        <v>17430</v>
+      </c>
+      <c r="C420" t="n">
+        <v>256950</v>
+      </c>
+      <c r="D420" t="n">
+        <v>18556</v>
+      </c>
+      <c r="E420" t="n">
+        <v>18249</v>
+      </c>
+      <c r="F420" t="n">
+        <v>17466</v>
+      </c>
+      <c r="G420" t="n">
+        <v>18091</v>
+      </c>
+      <c r="H420" t="n">
+        <v>-0.1096510655051922</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -11337,25 +11337,25 @@
         <v>46287</v>
       </c>
       <c r="B421" t="n">
-        <v>17430</v>
+        <v>17630</v>
       </c>
       <c r="C421" t="n">
-        <v>29548</v>
+        <v>222218</v>
       </c>
       <c r="D421" t="n">
-        <v>18554</v>
+        <v>18543</v>
       </c>
       <c r="E421" t="n">
-        <v>18246</v>
+        <v>18233</v>
       </c>
       <c r="F421" t="n">
-        <v>17400</v>
+        <v>17412</v>
       </c>
       <c r="G421" t="n">
-        <v>18067</v>
+        <v>18063</v>
       </c>
       <c r="H421" t="n">
-        <v>-0.1108322259953738</v>
+        <v>-0.1110290860770707</v>
       </c>
     </row>
   </sheetData>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H421"/>
+  <dimension ref="A1:H422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11358,6 +11358,32 @@
         <v>-0.1110290860770707</v>
       </c>
     </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B422" t="n">
+        <v>17680</v>
+      </c>
+      <c r="C422" t="n">
+        <v>175258</v>
+      </c>
+      <c r="D422" t="n">
+        <v>18529</v>
+      </c>
+      <c r="E422" t="n">
+        <v>18222</v>
+      </c>
+      <c r="F422" t="n">
+        <v>17372</v>
+      </c>
+      <c r="G422" t="n">
+        <v>18041</v>
+      </c>
+      <c r="H422" t="n">
+        <v>-0.1121118165264039</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H422"/>
+  <dimension ref="A1:H423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11384,6 +11384,32 @@
         <v>-0.1121118165264039</v>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B423" t="n">
+        <v>17810</v>
+      </c>
+      <c r="C423" t="n">
+        <v>228489</v>
+      </c>
+      <c r="D423" t="n">
+        <v>18494</v>
+      </c>
+      <c r="E423" t="n">
+        <v>18052</v>
+      </c>
+      <c r="F423" t="n">
+        <v>17408</v>
+      </c>
+      <c r="G423" t="n">
+        <v>17985</v>
+      </c>
+      <c r="H423" t="n">
+        <v>-0.1148678576701609</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H423"/>
+  <dimension ref="A1:H424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11410,6 +11410,32 @@
         <v>-0.1148678576701609</v>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B424" t="n">
+        <v>17880</v>
+      </c>
+      <c r="C424" t="n">
+        <v>174432</v>
+      </c>
+      <c r="D424" t="n">
+        <v>18474</v>
+      </c>
+      <c r="E424" t="n">
+        <v>18049</v>
+      </c>
+      <c r="F424" t="n">
+        <v>17670</v>
+      </c>
+      <c r="G424" t="n">
+        <v>18064</v>
+      </c>
+      <c r="H424" t="n">
+        <v>-0.1109798710566465</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H424"/>
+  <dimension ref="A1:H425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11436,6 +11436,32 @@
         <v>-0.1109798710566465</v>
       </c>
     </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B425" t="n">
+        <v>18740</v>
+      </c>
+      <c r="C425" t="n">
+        <v>1140803</v>
+      </c>
+      <c r="D425" t="n">
+        <v>18454</v>
+      </c>
+      <c r="E425" t="n">
+        <v>18100</v>
+      </c>
+      <c r="F425" t="n">
+        <v>18330</v>
+      </c>
+      <c r="G425" t="n">
+        <v>18295</v>
+      </c>
+      <c r="H425" t="n">
+        <v>-0.09961120133864854</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H425"/>
+  <dimension ref="A1:H427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11462,6 +11462,58 @@
         <v>-0.09961120133864854</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B426" t="n">
+        <v>18740</v>
+      </c>
+      <c r="C426" t="n">
+        <v>383430</v>
+      </c>
+      <c r="D426" t="n">
+        <v>18462</v>
+      </c>
+      <c r="E426" t="n">
+        <v>18108</v>
+      </c>
+      <c r="F426" t="n">
+        <v>18479</v>
+      </c>
+      <c r="G426" t="n">
+        <v>18350</v>
+      </c>
+      <c r="H426" t="n">
+        <v>-0.0969043752153157</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B427" t="n">
+        <v>18700</v>
+      </c>
+      <c r="C427" t="n">
+        <v>208799</v>
+      </c>
+      <c r="D427" t="n">
+        <v>18465</v>
+      </c>
+      <c r="E427" t="n">
+        <v>18086</v>
+      </c>
+      <c r="F427" t="n">
+        <v>18566</v>
+      </c>
+      <c r="G427" t="n">
+        <v>18373</v>
+      </c>
+      <c r="H427" t="n">
+        <v>-0.09577242974555833</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H427"/>
+  <dimension ref="A1:H428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,32 @@
         <v>-0.09577242974555833</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B428" t="n">
+        <v>18650</v>
+      </c>
+      <c r="C428" t="n">
+        <v>307660</v>
+      </c>
+      <c r="D428" t="n">
+        <v>18437</v>
+      </c>
+      <c r="E428" t="n">
+        <v>18065</v>
+      </c>
+      <c r="F428" t="n">
+        <v>18656</v>
+      </c>
+      <c r="G428" t="n">
+        <v>18386</v>
+      </c>
+      <c r="H428" t="n">
+        <v>-0.09513263448004328</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H428"/>
+  <dimension ref="A1:H429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11540,6 +11540,32 @@
         <v>-0.09513263448004328</v>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B429" t="n">
+        <v>18960</v>
+      </c>
+      <c r="C429" t="n">
+        <v>352726</v>
+      </c>
+      <c r="D429" t="n">
+        <v>18427</v>
+      </c>
+      <c r="E429" t="n">
+        <v>18081</v>
+      </c>
+      <c r="F429" t="n">
+        <v>18757</v>
+      </c>
+      <c r="G429" t="n">
+        <v>18422</v>
+      </c>
+      <c r="H429" t="n">
+        <v>-0.09336089374477086</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H429"/>
+  <dimension ref="A1:H430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11566,32 @@
         <v>-0.09336089374477086</v>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B430" t="n">
+        <v>18820</v>
+      </c>
+      <c r="C430" t="n">
+        <v>433628</v>
+      </c>
+      <c r="D430" t="n">
+        <v>18439</v>
+      </c>
+      <c r="E430" t="n">
+        <v>18095</v>
+      </c>
+      <c r="F430" t="n">
+        <v>18785</v>
+      </c>
+      <c r="G430" t="n">
+        <v>18440</v>
+      </c>
+      <c r="H430" t="n">
+        <v>-0.09247502337713465</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H430"/>
+  <dimension ref="A1:H431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,32 @@
         <v>-0.09247502337713465</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B431" t="n">
+        <v>19310</v>
+      </c>
+      <c r="C431" t="n">
+        <v>613648</v>
+      </c>
+      <c r="D431" t="n">
+        <v>18449</v>
+      </c>
+      <c r="E431" t="n">
+        <v>18101</v>
+      </c>
+      <c r="F431" t="n">
+        <v>18962</v>
+      </c>
+      <c r="G431" t="n">
+        <v>18504</v>
+      </c>
+      <c r="H431" t="n">
+        <v>-0.08932526206998381</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H431"/>
+  <dimension ref="A1:H432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11618,6 +11618,32 @@
         <v>-0.08932526206998381</v>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B432" t="n">
+        <v>19440</v>
+      </c>
+      <c r="C432" t="n">
+        <v>502426</v>
+      </c>
+      <c r="D432" t="n">
+        <v>18472</v>
+      </c>
+      <c r="E432" t="n">
+        <v>18175</v>
+      </c>
+      <c r="F432" t="n">
+        <v>19096</v>
+      </c>
+      <c r="G432" t="n">
+        <v>18581</v>
+      </c>
+      <c r="H432" t="n">
+        <v>-0.08553570549731782</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H432"/>
+  <dimension ref="A1:H433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11644,6 +11644,32 @@
         <v>-0.08553570549731782</v>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B433" t="n">
+        <v>19320</v>
+      </c>
+      <c r="C433" t="n">
+        <v>249767</v>
+      </c>
+      <c r="D433" t="n">
+        <v>18475</v>
+      </c>
+      <c r="E433" t="n">
+        <v>18183</v>
+      </c>
+      <c r="F433" t="n">
+        <v>19185</v>
+      </c>
+      <c r="G433" t="n">
+        <v>18614</v>
+      </c>
+      <c r="H433" t="n">
+        <v>-0.08391160982331802</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H433"/>
+  <dimension ref="A1:H434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11670,6 +11670,32 @@
         <v>-0.08391160982331802</v>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B434" t="n">
+        <v>19390</v>
+      </c>
+      <c r="C434" t="n">
+        <v>442259</v>
+      </c>
+      <c r="D434" t="n">
+        <v>18502</v>
+      </c>
+      <c r="E434" t="n">
+        <v>18228</v>
+      </c>
+      <c r="F434" t="n">
+        <v>19261</v>
+      </c>
+      <c r="G434" t="n">
+        <v>18664</v>
+      </c>
+      <c r="H434" t="n">
+        <v>-0.08145085880210645</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H434"/>
+  <dimension ref="A1:H435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11696,6 +11696,32 @@
         <v>-0.08145085880210645</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B435" t="n">
+        <v>19490</v>
+      </c>
+      <c r="C435" t="n">
+        <v>374550</v>
+      </c>
+      <c r="D435" t="n">
+        <v>18527</v>
+      </c>
+      <c r="E435" t="n">
+        <v>18381</v>
+      </c>
+      <c r="F435" t="n">
+        <v>19388</v>
+      </c>
+      <c r="G435" t="n">
+        <v>18765</v>
+      </c>
+      <c r="H435" t="n">
+        <v>-0.07648014173925877</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H435"/>
+  <dimension ref="A1:H436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11722,6 +11722,32 @@
         <v>-0.07648014173925877</v>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B436" t="n">
+        <v>19900</v>
+      </c>
+      <c r="C436" t="n">
+        <v>280227</v>
+      </c>
+      <c r="D436" t="n">
+        <v>18543</v>
+      </c>
+      <c r="E436" t="n">
+        <v>18848</v>
+      </c>
+      <c r="F436" t="n">
+        <v>19492</v>
+      </c>
+      <c r="G436" t="n">
+        <v>18961</v>
+      </c>
+      <c r="H436" t="n">
+        <v>-0.0668339977361091</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H436"/>
+  <dimension ref="A1:H437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11748,6 +11748,32 @@
         <v>-0.0668339977361091</v>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B437" t="n">
+        <v>19750</v>
+      </c>
+      <c r="C437" t="n">
+        <v>267582</v>
+      </c>
+      <c r="D437" t="n">
+        <v>18561</v>
+      </c>
+      <c r="E437" t="n">
+        <v>18884</v>
+      </c>
+      <c r="F437" t="n">
+        <v>19551</v>
+      </c>
+      <c r="G437" t="n">
+        <v>18999</v>
+      </c>
+      <c r="H437" t="n">
+        <v>-0.06496382695998815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H437"/>
+  <dimension ref="A1:H438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11774,6 +11774,32 @@
         <v>-0.06496382695998815</v>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B438" t="n">
+        <v>19570</v>
+      </c>
+      <c r="C438" t="n">
+        <v>329971</v>
+      </c>
+      <c r="D438" t="n">
+        <v>18575</v>
+      </c>
+      <c r="E438" t="n">
+        <v>18974</v>
+      </c>
+      <c r="F438" t="n">
+        <v>19588</v>
+      </c>
+      <c r="G438" t="n">
+        <v>19046</v>
+      </c>
+      <c r="H438" t="n">
+        <v>-0.0626507210000492</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H438"/>
+  <dimension ref="A1:H439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11800,6 +11800,32 @@
         <v>-0.0626507210000492</v>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B439" t="n">
+        <v>19580</v>
+      </c>
+      <c r="C439" t="n">
+        <v>405391</v>
+      </c>
+      <c r="D439" t="n">
+        <v>18602</v>
+      </c>
+      <c r="E439" t="n">
+        <v>19053</v>
+      </c>
+      <c r="F439" t="n">
+        <v>19639</v>
+      </c>
+      <c r="G439" t="n">
+        <v>19098</v>
+      </c>
+      <c r="H439" t="n">
+        <v>-0.0600915399379891</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H439"/>
+  <dimension ref="A1:H440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11826,6 +11826,32 @@
         <v>-0.0600915399379891</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B440" t="n">
+        <v>19390</v>
+      </c>
+      <c r="C440" t="n">
+        <v>285330</v>
+      </c>
+      <c r="D440" t="n">
+        <v>18616</v>
+      </c>
+      <c r="E440" t="n">
+        <v>19101</v>
+      </c>
+      <c r="F440" t="n">
+        <v>19630</v>
+      </c>
+      <c r="G440" t="n">
+        <v>19116</v>
+      </c>
+      <c r="H440" t="n">
+        <v>-0.05920566957035289</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H440"/>
+  <dimension ref="A1:H441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11852,6 +11852,32 @@
         <v>-0.05920566957035289</v>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B441" t="n">
+        <v>19170</v>
+      </c>
+      <c r="C441" t="n">
+        <v>235792</v>
+      </c>
+      <c r="D441" t="n">
+        <v>18602</v>
+      </c>
+      <c r="E441" t="n">
+        <v>19104</v>
+      </c>
+      <c r="F441" t="n">
+        <v>19509</v>
+      </c>
+      <c r="G441" t="n">
+        <v>19071</v>
+      </c>
+      <c r="H441" t="n">
+        <v>-0.06142034548944342</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H441"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11878,6 +11878,32 @@
         <v>-0.06142034548944342</v>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B442" t="n">
+        <v>19010</v>
+      </c>
+      <c r="C442" t="n">
+        <v>242288</v>
+      </c>
+      <c r="D442" t="n">
+        <v>18601</v>
+      </c>
+      <c r="E442" t="n">
+        <v>19101</v>
+      </c>
+      <c r="F442" t="n">
+        <v>19385</v>
+      </c>
+      <c r="G442" t="n">
+        <v>19029</v>
+      </c>
+      <c r="H442" t="n">
+        <v>-0.0634873763472612</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H442"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11904,6 +11904,32 @@
         <v>-0.0634873763472612</v>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B443" t="n">
+        <v>18510</v>
+      </c>
+      <c r="C443" t="n">
+        <v>498363</v>
+      </c>
+      <c r="D443" t="n">
+        <v>18583</v>
+      </c>
+      <c r="E443" t="n">
+        <v>19101</v>
+      </c>
+      <c r="F443" t="n">
+        <v>19087</v>
+      </c>
+      <c r="G443" t="n">
+        <v>18923</v>
+      </c>
+      <c r="H443" t="n">
+        <v>-0.06870416851222994</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H443"/>
+  <dimension ref="A1:H444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11930,6 +11930,32 @@
         <v>-0.06870416851222994</v>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B444" t="n">
+        <v>18780</v>
+      </c>
+      <c r="C444" t="n">
+        <v>427051</v>
+      </c>
+      <c r="D444" t="n">
+        <v>18588</v>
+      </c>
+      <c r="E444" t="n">
+        <v>19110</v>
+      </c>
+      <c r="F444" t="n">
+        <v>18891</v>
+      </c>
+      <c r="G444" t="n">
+        <v>18863</v>
+      </c>
+      <c r="H444" t="n">
+        <v>-0.07165706973768393</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/제일기획_일별_기준주가.xlsx
+++ b/data/제일기획_일별_기준주가.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H444"/>
+  <dimension ref="A1:H445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11956,6 +11956,32 @@
         <v>-0.07165706973768393</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B445" t="n">
+        <v>18380</v>
+      </c>
+      <c r="C445" t="n">
+        <v>400533</v>
+      </c>
+      <c r="D445" t="n">
+        <v>18583</v>
+      </c>
+      <c r="E445" t="n">
+        <v>19128</v>
+      </c>
+      <c r="F445" t="n">
+        <v>18698</v>
+      </c>
+      <c r="G445" t="n">
+        <v>18803</v>
+      </c>
+      <c r="H445" t="n">
+        <v>-0.07460997096313793</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
